--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T22:56:55+00:00</t>
+    <t>2026-06-16T23:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T23:15:28+00:00</t>
+    <t>2026-06-16T23:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T23:27:01+00:00</t>
+    <t>2026-06-17T00:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:00:17+00:00</t>
+    <t>2026-06-17T00:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:17:01+00:00</t>
+    <t>2026-06-17T00:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:28:17+00:00</t>
+    <t>2026-06-17T00:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:35:38+00:00</t>
+    <t>2026-06-17T04:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T04:31:39+00:00</t>
+    <t>2026-06-17T05:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T05:47:03+00:00</t>
+    <t>2026-06-17T10:39:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T10:39:22+00:00</t>
+    <t>2026-06-17T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-service-request.xlsx
+++ b/dev/StructureDefinition-ereferral-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T12:31:02+00:00</t>
+    <t>2026-07-07T09:49:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
